--- a/Employee_Reports_wi48/Willie Facun Adi Q0370.xlsx
+++ b/Employee_Reports_wi48/Willie Facun Adi Q0370.xlsx
@@ -566,11 +566,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-181</v>
+        <v>-184</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
